--- a/google-sheets/Fichas_participacion.xlsx
+++ b/google-sheets/Fichas_participacion.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -455,7 +455,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Esta hoja guarda las fichas de la app «Fichas de participación» (versión GitHub).</t>
+          <t>Esta hoja guarda las asignaturas, fichas y preguntas de la app «Fichas de participación».</t>
         </is>
       </c>
     </row>
@@ -486,14 +486,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2. Borra lo que haya y pega el contenido del archivo google-sheets/Codigo.gs del zip.</t>
+          <t>2. Borra lo que haya y pega el contenido del archivo google-sheets/Codigo.gs.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3. En la línea const CLAVE = 'CAMBIA-ESTA-CLAVE'; pon una palabra secreta tuya y guarda (icono del disquete).</t>
+          <t>3. En la línea const CLAVE = 'CAMBIA-ESTA-CLAVE'; escribe tu contraseña y guarda (icono del disquete).</t>
         </is>
       </c>
     </row>
@@ -514,55 +514,62 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5. Copia la URL que termina en /exec.</t>
+          <t>5. Copia la dirección que termina en /exec.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6. En la app: Inicio → Dónde se guardan los datos → Google Sheets → pega la URL y la clave → Conectar.</t>
+          <t>6. En la app: Conectar con hoja de cálculo → Configurar ahora → paso 5: pega la dirección y tu contraseña → Probar y entrar.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>7. Opcional: descarga config.js desde la app y súbelo a tu repositorio para que en el aula solo pida la contraseña.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Pestañas</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Notas: fichas y puntos de cada estudiante por parcial (se reescribe en cada guardado).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Registro: fecha y hora de cada participación.</t>
+          <t>Notas: fichas, puntos y respuestas de cada estudiante por parcial (se reescribe en cada guardado).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Registro: fecha, hora, resultado y pregunta de cada participación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>_datos (oculta): copia completa del curso que usa la app. No la edites a mano.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-    </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Si cambias el código del script, usa Implementar → Gestionar implementaciones → editar → Nueva versión para mantener la misma URL.</t>
+      <c r="A20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Si cambias el código del script, usa Implementar → Gestionar implementaciones → editar → Nueva versión para mantener la misma dirección.</t>
         </is>
       </c>
     </row>
@@ -577,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -590,6 +597,8 @@
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -641,6 +650,16 @@
       <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Total puntos</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Respuestas correctas</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Respuestas incorrectas</t>
         </is>
       </c>
     </row>
@@ -655,7 +674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -664,6 +683,9 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -695,6 +717,21 @@
       <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Fecha y hora</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Tema</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Pregunta</t>
         </is>
       </c>
     </row>
